--- a/ig/test-tabs-svs/ValueSet-vs-tre-r383-mention-act-de-soin-amm-all.xlsx
+++ b/ig/test-tabs-svs/ValueSet-vs-tre-r383-mention-act-de-soin-amm-all.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -106,6 +108,513 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r383-mention-act-de-soin-amm</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r383-mention-act-de-soin-amm|20260330120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ME014</t>
+  </si>
+  <si>
+    <t>A - Actes de prise en charge des anomalies du cloisonnement inter atrial, fermeture du canal artériel, dilatation de sténose valvulaire pulmonaire, cathétérisme diagnostique des cardiopathies congénitales</t>
+  </si>
+  <si>
+    <t>ME009</t>
+  </si>
+  <si>
+    <t>A - Actes interventionnels d’électrophysiologie diagnostique et les actes de poses de pace maker mono et double chambre avec sonde</t>
+  </si>
+  <si>
+    <t>ME038</t>
+  </si>
+  <si>
+    <t>A - Radiothérapie externe chez l’adulte</t>
+  </si>
+  <si>
+    <t>ME005</t>
+  </si>
+  <si>
+    <t>A - Thrombectomie mécanique</t>
+  </si>
+  <si>
+    <t>ME042</t>
+  </si>
+  <si>
+    <t>A - TMSC chez l'adulte</t>
+  </si>
+  <si>
+    <t>ME025</t>
+  </si>
+  <si>
+    <t>A1 - Chirurgie oncologique viscérale et digestive</t>
+  </si>
+  <si>
+    <t>ME026</t>
+  </si>
+  <si>
+    <t>A2 - Chirurgie oncologique thoracique</t>
+  </si>
+  <si>
+    <t>ME027</t>
+  </si>
+  <si>
+    <t>A3 - Chirurgie oncologiqueORL, cervico-faciale et maxillo-faciale, dont la chirurgie du cancer de la thyroïde</t>
+  </si>
+  <si>
+    <t>ME028</t>
+  </si>
+  <si>
+    <t>A4 - Chirurgie oncologique urologique</t>
+  </si>
+  <si>
+    <t>ME029</t>
+  </si>
+  <si>
+    <t>A5 - Chirurgie oncologique gynécologique</t>
+  </si>
+  <si>
+    <t>ME030</t>
+  </si>
+  <si>
+    <t>A6 - Chirurgie oncologique mammaire</t>
+  </si>
+  <si>
+    <t>ME031</t>
+  </si>
+  <si>
+    <t>A7 - Chirurgie oncologique indifférenciée</t>
+  </si>
+  <si>
+    <t>ME065</t>
+  </si>
+  <si>
+    <t>Adulte et pédiatrique</t>
+  </si>
+  <si>
+    <t>ME089</t>
+  </si>
+  <si>
+    <t>Adultes</t>
+  </si>
+  <si>
+    <t>ME003</t>
+  </si>
+  <si>
+    <t>Ante et post partum</t>
+  </si>
+  <si>
+    <t>ME067</t>
+  </si>
+  <si>
+    <t>Antenne de SMUR</t>
+  </si>
+  <si>
+    <t>ME011</t>
+  </si>
+  <si>
+    <t>B - Actes d'ablation atriale droite et atrioventriculaire, de poses de défibrillateurs et de stimulateurs multisites</t>
+  </si>
+  <si>
+    <t>ME039</t>
+  </si>
+  <si>
+    <t>B - Curiethérapie chez l’adulte</t>
+  </si>
+  <si>
+    <t>ME006</t>
+  </si>
+  <si>
+    <t>B - Ensemble des activités de NRI</t>
+  </si>
+  <si>
+    <t>ME015</t>
+  </si>
+  <si>
+    <t>B - Geste de dilatation, toute pose de stent ou de dispositif intracardiaque, toute intervention sur septum atrial ou ventriculaire</t>
+  </si>
+  <si>
+    <t>ME043</t>
+  </si>
+  <si>
+    <t>B - TMSC chez l'adulte comprenant les chimiothérapies intensives entrainant une aplasie prévisible de plus de huit jours</t>
+  </si>
+  <si>
+    <t>ME032</t>
+  </si>
+  <si>
+    <t>B1 - Chirurgie oncologique viscérale et digestive complexe</t>
+  </si>
+  <si>
+    <t>ME033</t>
+  </si>
+  <si>
+    <t>B2 - Chirurgie oncologique thoracique complexe</t>
+  </si>
+  <si>
+    <t>ME034</t>
+  </si>
+  <si>
+    <t>B3 - Chirurgie oncologique ORL, cervico-faciale et maxillo-faciale complexe</t>
+  </si>
+  <si>
+    <t>ME035</t>
+  </si>
+  <si>
+    <t>B4 - Chirurgie oncologique urologique complexe</t>
+  </si>
+  <si>
+    <t>ME036</t>
+  </si>
+  <si>
+    <t>B5 - Chirurgie oncologique gynécologique complexe</t>
+  </si>
+  <si>
+    <t>ME057</t>
+  </si>
+  <si>
+    <t>Brûlés</t>
+  </si>
+  <si>
+    <t>ME012</t>
+  </si>
+  <si>
+    <t>C - Actes d'ablation atriale avec abord transeptal, d'ablation ventriculaire et tous les actes de rythmologie réalisés chez un enfant hors cardiopathie congénitale complexe</t>
+  </si>
+  <si>
+    <t>ME037</t>
+  </si>
+  <si>
+    <t>C - Chirurgie oncologique chez l'Enfant et les adolescents de moins de 18 ans</t>
+  </si>
+  <si>
+    <t>ME044</t>
+  </si>
+  <si>
+    <t>C - TMSC chez l'Enfant et l’adolescent de moins de 18 ans comprenant les chimiothérapie intensives entraînant une aplasie prévisible de plus de huit jours</t>
+  </si>
+  <si>
+    <t>ME040</t>
+  </si>
+  <si>
+    <t>C1 - Radiothérapie externe chez l'Enfant et l'adolescent de moins de 18 ans (en sus des mêmes traitements de radiothérapie externe chez l'adulte)</t>
+  </si>
+  <si>
+    <t>ME041</t>
+  </si>
+  <si>
+    <t>C2 - Curiethérapie chez l'Enfant et l'adolescent de moins de 18 ans (en sus des mêmes traitements de curiethérapie chez l'adulte)</t>
+  </si>
+  <si>
+    <t>ME053</t>
+  </si>
+  <si>
+    <t>Cardio-Vasculaire</t>
+  </si>
+  <si>
+    <t>ME088</t>
+  </si>
+  <si>
+    <t>Cellules hématopoïétiques Allogreffe</t>
+  </si>
+  <si>
+    <t>ME058</t>
+  </si>
+  <si>
+    <t>Conduites addictives</t>
+  </si>
+  <si>
+    <t>ME085</t>
+  </si>
+  <si>
+    <t>Cœur</t>
+  </si>
+  <si>
+    <t>ME087</t>
+  </si>
+  <si>
+    <t>Cœur-poumon</t>
+  </si>
+  <si>
+    <t>ME013</t>
+  </si>
+  <si>
+    <t>D - Actes à haut risque de plaie cardiaque ou vasculaire et les actes de rythmologie réalisés chez un patient ayant une cardiopathie congénitale complexe</t>
+  </si>
+  <si>
+    <t>ME090</t>
+  </si>
+  <si>
+    <t>Enfants</t>
+  </si>
+  <si>
+    <t>ME004</t>
+  </si>
+  <si>
+    <t>Enfants de moins de trois ans</t>
+  </si>
+  <si>
+    <t>ME060</t>
+  </si>
+  <si>
+    <t>Enfants et adolescents</t>
+  </si>
+  <si>
+    <t>ME083</t>
+  </si>
+  <si>
+    <t>Foie</t>
+  </si>
+  <si>
+    <t>ME059</t>
+  </si>
+  <si>
+    <t>Gériatrie</t>
+  </si>
+  <si>
+    <t>ME084</t>
+  </si>
+  <si>
+    <t>Intestin</t>
+  </si>
+  <si>
+    <t>ME061</t>
+  </si>
+  <si>
+    <t>Jeunes enfants, enfants et adolescents</t>
+  </si>
+  <si>
+    <t>ME051</t>
+  </si>
+  <si>
+    <t>Locomoteur</t>
+  </si>
+  <si>
+    <t>ME045</t>
+  </si>
+  <si>
+    <t>Mention A - Actes de radiologie interventionnelle par voie endo-veineuse</t>
+  </si>
+  <si>
+    <t>ME007</t>
+  </si>
+  <si>
+    <t>Mention A - Actes diagnostiques ou thérapeutiques hors pathologie cancéreuses réalisés par l'administration de mrp en système clos</t>
+  </si>
+  <si>
+    <t>ME008</t>
+  </si>
+  <si>
+    <t>Mention B - Actes diagnostiques ou thérapeutiques y compris pour les pathologies cancéreuses réalisés par l'administration de mrp en système clos ouvert</t>
+  </si>
+  <si>
+    <t>ME046</t>
+  </si>
+  <si>
+    <t>Mention B - En sus des actes autorisés au titre de la mention A</t>
+  </si>
+  <si>
+    <t>ME047</t>
+  </si>
+  <si>
+    <t>Mention C - En sus des actes autorisés au titre de la mention B et à l'Exception des actes réalisés dans les conditions spécifiquement prévues au titre de la mention D</t>
+  </si>
+  <si>
+    <t>ME048</t>
+  </si>
+  <si>
+    <t>Mention D - Ensemble des actes mentionnés à l'article R. 6123-165</t>
+  </si>
+  <si>
+    <t>ME062</t>
+  </si>
+  <si>
+    <t>Oncologie</t>
+  </si>
+  <si>
+    <t>ME056</t>
+  </si>
+  <si>
+    <t>Oncologie et hématologie</t>
+  </si>
+  <si>
+    <t>ME081</t>
+  </si>
+  <si>
+    <t>Pancréas</t>
+  </si>
+  <si>
+    <t>ME000</t>
+  </si>
+  <si>
+    <t>Pas de mention</t>
+  </si>
+  <si>
+    <t>ME054</t>
+  </si>
+  <si>
+    <t>Pneumologie</t>
+  </si>
+  <si>
+    <t>ME050</t>
+  </si>
+  <si>
+    <t>Polyvalent</t>
+  </si>
+  <si>
+    <t>ME086</t>
+  </si>
+  <si>
+    <t>Poumon</t>
+  </si>
+  <si>
+    <t>ME071</t>
+  </si>
+  <si>
+    <t>Psychaitrie périnatale</t>
+  </si>
+  <si>
+    <t>ME049</t>
+  </si>
+  <si>
+    <t>Psychiatrie de l'adulte</t>
+  </si>
+  <si>
+    <t>ME070</t>
+  </si>
+  <si>
+    <t>Psychiatrie de l'Enfant et adolescent</t>
+  </si>
+  <si>
+    <t>ME064</t>
+  </si>
+  <si>
+    <t>Pédiatrique</t>
+  </si>
+  <si>
+    <t>ME080</t>
+  </si>
+  <si>
+    <t>Rein</t>
+  </si>
+  <si>
+    <t>ME082</t>
+  </si>
+  <si>
+    <t>Rein-pancréas</t>
+  </si>
+  <si>
+    <t>ME002</t>
+  </si>
+  <si>
+    <t>Réadaptation</t>
+  </si>
+  <si>
+    <t>ME021</t>
+  </si>
+  <si>
+    <t>Réanimation de recours et soins intensifs pédiatriques polyvalents, et de spécialité le cas échéant</t>
+  </si>
+  <si>
+    <t>ME016</t>
+  </si>
+  <si>
+    <t>Réanimation et soins intensifs polyvalents, et de spécialité le cas échéant</t>
+  </si>
+  <si>
+    <t>ME022</t>
+  </si>
+  <si>
+    <t>Réanimation et soins intensifs pédiatriques polyvalents, et de spécialité le cas échéant</t>
+  </si>
+  <si>
+    <t>ME001</t>
+  </si>
+  <si>
+    <t>Socle</t>
+  </si>
+  <si>
+    <t>ME018</t>
+  </si>
+  <si>
+    <t>Soins intensifs de cardiologie</t>
+  </si>
+  <si>
+    <t>ME019</t>
+  </si>
+  <si>
+    <t>Soins intensifs de neurologie vasculaire</t>
+  </si>
+  <si>
+    <t>ME020</t>
+  </si>
+  <si>
+    <t>Soins intensifs d’hématologie</t>
+  </si>
+  <si>
+    <t>ME017</t>
+  </si>
+  <si>
+    <t>Soins intensifs polyvalents dérogatoires</t>
+  </si>
+  <si>
+    <t>ME024</t>
+  </si>
+  <si>
+    <t>Soins intensifs pédiatriques d’hématologie</t>
+  </si>
+  <si>
+    <t>ME023</t>
+  </si>
+  <si>
+    <t>Soins intensifs pédiatriques polyvalents dérogatoires</t>
+  </si>
+  <si>
+    <t>ME072</t>
+  </si>
+  <si>
+    <t>Soins sans consentement</t>
+  </si>
+  <si>
+    <t>ME055</t>
+  </si>
+  <si>
+    <t>Système digestif, endocrinologie, diabétologie, nutrition</t>
+  </si>
+  <si>
+    <t>ME052</t>
+  </si>
+  <si>
+    <t>Système nerveux</t>
   </si>
 </sst>
 </file>
@@ -397,4 +906,1730 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>